--- a/Formatos/Visita Extraordinaria GFPI-F023.xlsx
+++ b/Formatos/Visita Extraordinaria GFPI-F023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/834af06e427efe68/Documents/Seto 2026/sena/Manual SENA Etapa Productiva/manual-aprendiz-sena/Formatos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{BE778CA7-250F-4550-B2A8-B238D2344594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39A8E1DC-D01E-47AE-8BC8-37253ECF1F7A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363F5DF6-A38B-4E41-A740-E7B496CB2FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
   <si>
     <t>Información general</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>virtual</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -899,435 +902,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1335,9 +909,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1345,6 +916,359 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1357,37 +1281,109 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDD5555"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1412,21 +1408,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
+          <bgColor rgb="FFDD5555"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1807,804 +1789,804 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D1" s="138" t="s">
+      <c r="D1" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="140"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="141" t="s">
+      <c r="D2" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="142"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="27"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D3" s="143" t="s">
+      <c r="D3" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="145"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="30"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D4" s="141" t="s">
+      <c r="D4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="142"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="27"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D5" s="143" t="s">
+      <c r="D5" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
-      <c r="L5" s="144"/>
-      <c r="M5" s="145"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
     </row>
     <row r="6" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="146" t="s">
+      <c r="D6" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="147"/>
-      <c r="F6" s="148" t="b">
+      <c r="E6" s="32"/>
+      <c r="F6" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="149" t="s">
+      <c r="G6" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="147"/>
-      <c r="I6" s="147"/>
-      <c r="J6" s="148" t="b">
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="149" t="s">
+      <c r="K6" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="147"/>
-      <c r="M6" s="150" t="b">
+      <c r="L6" s="32"/>
+      <c r="M6" s="19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="13"/>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="120"/>
+      <c r="K8" s="120"/>
+      <c r="L8" s="120"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="120"/>
     </row>
     <row r="9" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="13"/>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="52" t="s">
+      <c r="D9" s="89"/>
+      <c r="E9" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="54"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="107"/>
     </row>
     <row r="10" spans="2:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="13"/>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="88" t="s">
+      <c r="D10" s="89"/>
+      <c r="E10" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="90"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="92"/>
       <c r="J10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="23"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="86"/>
+      <c r="N10" s="86"/>
+      <c r="O10" s="87"/>
     </row>
     <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="13"/>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="101" t="s">
+      <c r="D11" s="89"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="62"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="123"/>
     </row>
     <row r="12" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="13"/>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="48"/>
+      <c r="D12" s="89"/>
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="54"/>
-      <c r="H12" s="103" t="s">
+      <c r="G12" s="107"/>
+      <c r="H12" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="104"/>
+      <c r="I12" s="59"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="103" t="s">
+      <c r="K12" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="104"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="L12" s="59"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="125"/>
+      <c r="O12" s="126"/>
     </row>
     <row r="13" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13"/>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="92"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="91" t="s">
+      <c r="D13" s="89"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="92"/>
-      <c r="K13" s="93"/>
-      <c r="L13" s="151"/>
-      <c r="M13" s="152"/>
-      <c r="N13" s="152"/>
-      <c r="O13" s="153"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="129"/>
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13"/>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="59"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="113"/>
     </row>
     <row r="15" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="95" t="s">
+      <c r="C15" s="97"/>
+      <c r="D15" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="96"/>
-      <c r="F15" s="97"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="68"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="131"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="132"/>
     </row>
     <row r="16" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="46" t="s">
+      <c r="C16" s="97"/>
+      <c r="D16" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="59"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="113"/>
     </row>
     <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="13"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="46" t="s">
+      <c r="C17" s="97"/>
+      <c r="D17" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="59"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="113"/>
     </row>
     <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="46" t="s">
+      <c r="C18" s="97"/>
+      <c r="D18" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="59"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="113"/>
     </row>
     <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="13"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="46" t="s">
+      <c r="C19" s="97"/>
+      <c r="D19" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="59"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="113"/>
     </row>
     <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="13"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="46" t="s">
+      <c r="C20" s="97"/>
+      <c r="D20" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="51"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="110"/>
     </row>
     <row r="21" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="13"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="46" t="s">
+      <c r="C21" s="97"/>
+      <c r="D21" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="51"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="110"/>
     </row>
     <row r="22" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="13"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="46" t="s">
+      <c r="C22" s="98"/>
+      <c r="D22" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="51"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="110"/>
     </row>
     <row r="23" spans="2:15" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="13"/>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="75" t="s">
+      <c r="E23" s="99"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="77"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="116"/>
+      <c r="L23" s="116"/>
+      <c r="M23" s="116"/>
+      <c r="N23" s="116"/>
+      <c r="O23" s="117"/>
     </row>
     <row r="24" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="13"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="46" t="s">
+      <c r="C24" s="97"/>
+      <c r="D24" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="80"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="76"/>
+      <c r="M24" s="76"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="77"/>
     </row>
     <row r="25" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="13"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="46" t="s">
+      <c r="C25" s="98"/>
+      <c r="D25" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="75" t="s">
+      <c r="E25" s="99"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="77"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="116"/>
+      <c r="L25" s="116"/>
+      <c r="M25" s="116"/>
+      <c r="N25" s="116"/>
+      <c r="O25" s="117"/>
     </row>
     <row r="26" spans="2:15" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="13"/>
       <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D26" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="59"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="113"/>
     </row>
     <row r="27" spans="2:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="13"/>
       <c r="C27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="59"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="113"/>
     </row>
     <row r="28" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="13"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="59"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="112"/>
+      <c r="J28" s="112"/>
+      <c r="K28" s="112"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="113"/>
     </row>
     <row r="29" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="13"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="59"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="112"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="113"/>
     </row>
     <row r="30" spans="2:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="13"/>
       <c r="C30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="46" t="s">
+      <c r="D30" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="59"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="112"/>
+      <c r="J30" s="112"/>
+      <c r="K30" s="112"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="113"/>
     </row>
     <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="13"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="46" t="s">
+      <c r="D31" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="47"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="59"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="113"/>
     </row>
     <row r="32" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="13"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="51"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="109"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="109"/>
+      <c r="L32" s="109"/>
+      <c r="M32" s="109"/>
+      <c r="N32" s="109"/>
+      <c r="O32" s="110"/>
     </row>
     <row r="33" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="13"/>
       <c r="C33" s="6"/>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="47"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="59"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="111"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
+      <c r="J33" s="112"/>
+      <c r="K33" s="112"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="113"/>
     </row>
     <row r="34" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="13"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="69" t="s">
+      <c r="D34" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="70"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="51"/>
+      <c r="E34" s="134"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="109"/>
+      <c r="J34" s="109"/>
+      <c r="K34" s="109"/>
+      <c r="L34" s="109"/>
+      <c r="M34" s="109"/>
+      <c r="N34" s="109"/>
+      <c r="O34" s="110"/>
     </row>
     <row r="35" spans="2:15" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="13"/>
       <c r="C35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="43" t="s">
+      <c r="D35" s="156" t="s">
         <v>41</v>
       </c>
-      <c r="E35" s="44"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="51"/>
+      <c r="E35" s="157"/>
+      <c r="F35" s="158"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="109"/>
+      <c r="J35" s="109"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="109"/>
+      <c r="M35" s="109"/>
+      <c r="N35" s="109"/>
+      <c r="O35" s="110"/>
     </row>
     <row r="36" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="13"/>
       <c r="C36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="51"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="109"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="109"/>
+      <c r="M36" s="109"/>
+      <c r="N36" s="109"/>
+      <c r="O36" s="110"/>
     </row>
     <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="13"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="46" t="s">
+      <c r="D37" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="51"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="109"/>
+      <c r="K37" s="109"/>
+      <c r="L37" s="109"/>
+      <c r="M37" s="109"/>
+      <c r="N37" s="109"/>
+      <c r="O37" s="110"/>
     </row>
     <row r="38" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="13"/>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
+      <c r="D38" s="136"/>
+      <c r="E38" s="136"/>
+      <c r="F38" s="136"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="136"/>
+      <c r="I38" s="136"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="136"/>
+      <c r="L38" s="136"/>
+      <c r="M38" s="136"/>
+      <c r="N38" s="136"/>
+      <c r="O38" s="136"/>
     </row>
     <row r="39" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
+      <c r="C39" s="136"/>
+      <c r="D39" s="136"/>
+      <c r="E39" s="136"/>
+      <c r="F39" s="136"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="136"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="136"/>
+      <c r="L39" s="136"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="136"/>
+      <c r="O39" s="136"/>
     </row>
     <row r="40" spans="2:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="13"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
+      <c r="C40" s="136"/>
+      <c r="D40" s="136"/>
+      <c r="E40" s="136"/>
+      <c r="F40" s="136"/>
+      <c r="G40" s="136"/>
+      <c r="H40" s="136"/>
+      <c r="I40" s="136"/>
+      <c r="J40" s="136"/>
+      <c r="K40" s="136"/>
+      <c r="L40" s="136"/>
+      <c r="M40" s="136"/>
+      <c r="N40" s="136"/>
+      <c r="O40" s="136"/>
     </row>
     <row r="41" spans="2:15" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="13"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="123" t="s">
+      <c r="D41" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="E41" s="123"/>
-      <c r="F41" s="123"/>
-      <c r="G41" s="123"/>
-      <c r="H41" s="123"/>
-      <c r="I41" s="123"/>
-      <c r="J41" s="123"/>
-      <c r="K41" s="123"/>
-      <c r="L41" s="123"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
       <c r="O41" s="11"/>
     </row>
     <row r="42" spans="2:15" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="144" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="32"/>
-      <c r="F42" s="154"/>
-      <c r="G42" s="156"/>
-      <c r="H42" s="35" t="s">
+      <c r="E42" s="145"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I42" s="36"/>
-      <c r="J42" s="154"/>
-      <c r="K42" s="155"/>
-      <c r="L42" s="156"/>
+      <c r="I42" s="147"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="74"/>
     </row>
     <row r="43" spans="2:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="157" t="s">
+      <c r="E43" s="145"/>
+      <c r="F43" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="G43" s="37" t="s">
+      <c r="G43" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="H43" s="38"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="42"/>
-      <c r="L43" s="34"/>
+      <c r="H43" s="149"/>
+      <c r="I43" s="147"/>
+      <c r="J43" s="153"/>
+      <c r="K43" s="154"/>
+      <c r="L43" s="155"/>
     </row>
     <row r="44" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="144" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="32"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="40"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="41"/>
+      <c r="E44" s="145"/>
+      <c r="F44" s="150"/>
+      <c r="G44" s="151"/>
+      <c r="H44" s="151"/>
+      <c r="I44" s="151"/>
+      <c r="J44" s="151"/>
+      <c r="K44" s="151"/>
+      <c r="L44" s="152"/>
     </row>
     <row r="45" spans="2:15" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="13"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="124" t="s">
+      <c r="D46" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="125"/>
-      <c r="F46" s="125"/>
-      <c r="G46" s="125"/>
-      <c r="H46" s="125"/>
-      <c r="I46" s="125"/>
-      <c r="J46" s="125"/>
-      <c r="K46" s="125"/>
-      <c r="L46" s="126"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="71"/>
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
       <c r="O46" s="11"/>
@@ -2612,21 +2594,21 @@
     <row r="47" spans="2:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="13"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="118" t="s">
+      <c r="D47" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="E47" s="119"/>
-      <c r="F47" s="103" t="s">
+      <c r="E47" s="54"/>
+      <c r="F47" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="G47" s="120"/>
-      <c r="H47" s="120"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="105" t="s">
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="K47" s="109"/>
-      <c r="L47" s="106"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="62"/>
       <c r="M47" s="11"/>
       <c r="N47" s="11"/>
       <c r="O47" s="11"/>
@@ -2634,19 +2616,19 @@
     <row r="48" spans="2:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="13"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="101"/>
-      <c r="E48" s="102"/>
-      <c r="F48" s="121" t="s">
+      <c r="D48" s="55"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="G48" s="122"/>
-      <c r="H48" s="121" t="s">
+      <c r="G48" s="67"/>
+      <c r="H48" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="I48" s="122"/>
-      <c r="J48" s="107"/>
-      <c r="K48" s="110"/>
-      <c r="L48" s="108"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="64"/>
+      <c r="L48" s="65"/>
       <c r="M48" s="11"/>
       <c r="N48" s="11"/>
       <c r="O48" s="11"/>
@@ -2654,17 +2636,17 @@
     <row r="49" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="13"/>
       <c r="C49" s="14"/>
-      <c r="D49" s="84" t="s">
+      <c r="D49" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="85"/>
-      <c r="F49" s="86"/>
-      <c r="G49" s="87"/>
-      <c r="H49" s="86"/>
-      <c r="I49" s="87"/>
-      <c r="J49" s="81"/>
-      <c r="K49" s="82"/>
-      <c r="L49" s="83"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="42"/>
       <c r="M49" s="14"/>
       <c r="N49" s="14"/>
       <c r="O49" s="14"/>
@@ -2672,17 +2654,17 @@
     <row r="50" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="13"/>
       <c r="C50" s="14"/>
-      <c r="D50" s="84" t="s">
+      <c r="D50" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="E50" s="85"/>
-      <c r="F50" s="86"/>
-      <c r="G50" s="87"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="25"/>
-      <c r="J50" s="81"/>
-      <c r="K50" s="82"/>
-      <c r="L50" s="83"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="137"/>
+      <c r="I50" s="138"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="41"/>
+      <c r="L50" s="42"/>
       <c r="M50" s="14"/>
       <c r="N50" s="14"/>
       <c r="O50" s="14"/>
@@ -2690,17 +2672,17 @@
     <row r="51" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="13"/>
       <c r="C51" s="14"/>
-      <c r="D51" s="84" t="s">
+      <c r="D51" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="E51" s="85"/>
-      <c r="F51" s="86"/>
-      <c r="G51" s="87"/>
-      <c r="H51" s="86"/>
-      <c r="I51" s="87"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="82"/>
-      <c r="L51" s="83"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="42"/>
       <c r="M51" s="14"/>
       <c r="N51" s="14"/>
       <c r="O51" s="14"/>
@@ -2708,17 +2690,17 @@
     <row r="52" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="13"/>
       <c r="C52" s="14"/>
-      <c r="D52" s="127" t="s">
+      <c r="D52" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="E52" s="128"/>
-      <c r="F52" s="116"/>
-      <c r="G52" s="117"/>
-      <c r="H52" s="116"/>
-      <c r="I52" s="117"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="23"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="84"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="84"/>
+      <c r="J52" s="85"/>
+      <c r="K52" s="86"/>
+      <c r="L52" s="87"/>
       <c r="M52" s="14"/>
       <c r="N52" s="14"/>
       <c r="O52" s="14"/>
@@ -2726,17 +2708,17 @@
     <row r="53" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="13"/>
       <c r="C53" s="14"/>
-      <c r="D53" s="84" t="s">
+      <c r="D53" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E53" s="85"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="87"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="87"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="82"/>
-      <c r="L53" s="83"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="41"/>
+      <c r="L53" s="42"/>
       <c r="M53" s="14"/>
       <c r="N53" s="14"/>
       <c r="O53" s="14"/>
@@ -2744,17 +2726,17 @@
     <row r="54" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="13"/>
       <c r="C54" s="14"/>
-      <c r="D54" s="84" t="s">
+      <c r="D54" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E54" s="85"/>
-      <c r="F54" s="86"/>
-      <c r="G54" s="87"/>
-      <c r="H54" s="86"/>
-      <c r="I54" s="87"/>
-      <c r="J54" s="81"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="83"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="42"/>
       <c r="M54" s="14"/>
       <c r="N54" s="14"/>
       <c r="O54" s="14"/>
@@ -2762,17 +2744,17 @@
     <row r="55" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="13"/>
       <c r="C55" s="14"/>
-      <c r="D55" s="84" t="s">
+      <c r="D55" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E55" s="85"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="87"/>
-      <c r="H55" s="86"/>
-      <c r="I55" s="87"/>
-      <c r="J55" s="81"/>
-      <c r="K55" s="82"/>
-      <c r="L55" s="83"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="42"/>
       <c r="M55" s="14"/>
       <c r="N55" s="14"/>
       <c r="O55" s="14"/>
@@ -2780,17 +2762,17 @@
     <row r="56" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="13"/>
       <c r="C56" s="14"/>
-      <c r="D56" s="129" t="s">
+      <c r="D56" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="E56" s="130"/>
-      <c r="F56" s="131"/>
-      <c r="G56" s="132"/>
-      <c r="H56" s="131"/>
-      <c r="I56" s="132"/>
-      <c r="J56" s="133"/>
-      <c r="K56" s="134"/>
-      <c r="L56" s="135"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="51"/>
+      <c r="L56" s="52"/>
       <c r="M56" s="14"/>
       <c r="N56" s="14"/>
       <c r="O56" s="14"/>
@@ -2798,17 +2780,17 @@
     <row r="57" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="13"/>
       <c r="C57" s="14"/>
-      <c r="D57" s="113" t="s">
+      <c r="D57" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="E57" s="114"/>
-      <c r="F57" s="114"/>
-      <c r="G57" s="114"/>
-      <c r="H57" s="114"/>
-      <c r="I57" s="114"/>
-      <c r="J57" s="114"/>
-      <c r="K57" s="114"/>
-      <c r="L57" s="115"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="82"/>
       <c r="M57" s="14"/>
       <c r="N57" s="14"/>
       <c r="O57" s="14"/>
@@ -2816,21 +2798,21 @@
     <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="13"/>
       <c r="C58" s="14"/>
-      <c r="D58" s="105" t="s">
+      <c r="D58" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="E58" s="106"/>
-      <c r="F58" s="78" t="s">
+      <c r="E58" s="62"/>
+      <c r="F58" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="G58" s="79"/>
-      <c r="H58" s="79"/>
-      <c r="I58" s="80"/>
-      <c r="J58" s="105" t="s">
+      <c r="G58" s="76"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="K58" s="109"/>
-      <c r="L58" s="106"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="62"/>
       <c r="M58" s="14"/>
       <c r="N58" s="14"/>
       <c r="O58" s="14"/>
@@ -2838,19 +2820,19 @@
     <row r="59" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="13"/>
       <c r="C59" s="14"/>
-      <c r="D59" s="107"/>
-      <c r="E59" s="108"/>
-      <c r="F59" s="111" t="s">
+      <c r="D59" s="63"/>
+      <c r="E59" s="65"/>
+      <c r="F59" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="G59" s="112"/>
-      <c r="H59" s="111" t="s">
+      <c r="G59" s="79"/>
+      <c r="H59" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="I59" s="112"/>
-      <c r="J59" s="107"/>
-      <c r="K59" s="110"/>
-      <c r="L59" s="108"/>
+      <c r="I59" s="79"/>
+      <c r="J59" s="63"/>
+      <c r="K59" s="64"/>
+      <c r="L59" s="65"/>
       <c r="M59" s="14"/>
       <c r="N59" s="14"/>
       <c r="O59" s="14"/>
@@ -2858,17 +2840,17 @@
     <row r="60" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="13"/>
       <c r="C60" s="14"/>
-      <c r="D60" s="84" t="s">
+      <c r="D60" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="E60" s="85"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="87"/>
-      <c r="H60" s="86"/>
-      <c r="I60" s="87"/>
-      <c r="J60" s="81"/>
-      <c r="K60" s="82"/>
-      <c r="L60" s="83"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="41"/>
+      <c r="L60" s="42"/>
       <c r="M60" s="14"/>
       <c r="N60" s="14"/>
       <c r="O60" s="14"/>
@@ -2876,17 +2858,17 @@
     <row r="61" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="13"/>
       <c r="C61" s="14"/>
-      <c r="D61" s="84" t="s">
+      <c r="D61" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="85"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="87"/>
-      <c r="H61" s="86"/>
-      <c r="I61" s="87"/>
-      <c r="J61" s="81"/>
-      <c r="K61" s="82"/>
-      <c r="L61" s="83"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="41"/>
+      <c r="L61" s="42"/>
       <c r="M61" s="14"/>
       <c r="N61" s="14"/>
       <c r="O61" s="14"/>
@@ -2894,17 +2876,17 @@
     <row r="62" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="13"/>
       <c r="C62" s="14"/>
-      <c r="D62" s="84" t="s">
+      <c r="D62" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="E62" s="85"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="87"/>
-      <c r="H62" s="86"/>
-      <c r="I62" s="87"/>
-      <c r="J62" s="81"/>
-      <c r="K62" s="82"/>
-      <c r="L62" s="83"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="41"/>
+      <c r="L62" s="42"/>
       <c r="M62" s="14"/>
       <c r="N62" s="14"/>
       <c r="O62" s="14"/>
@@ -2912,17 +2894,17 @@
     <row r="63" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="13"/>
       <c r="C63" s="14"/>
-      <c r="D63" s="84" t="s">
+      <c r="D63" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="E63" s="85"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="87"/>
-      <c r="H63" s="86"/>
-      <c r="I63" s="87"/>
-      <c r="J63" s="81"/>
-      <c r="K63" s="82"/>
-      <c r="L63" s="83"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="39"/>
+      <c r="J63" s="40"/>
+      <c r="K63" s="41"/>
+      <c r="L63" s="42"/>
       <c r="M63" s="14"/>
       <c r="N63" s="14"/>
       <c r="O63" s="14"/>
@@ -2930,17 +2912,17 @@
     <row r="64" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="13"/>
       <c r="C64" s="14"/>
-      <c r="D64" s="84" t="s">
+      <c r="D64" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="E64" s="85"/>
-      <c r="F64" s="86"/>
-      <c r="G64" s="87"/>
-      <c r="H64" s="86"/>
-      <c r="I64" s="87"/>
-      <c r="J64" s="81"/>
-      <c r="K64" s="82"/>
-      <c r="L64" s="83"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="41"/>
+      <c r="L64" s="42"/>
       <c r="M64" s="14"/>
       <c r="N64" s="14"/>
       <c r="O64" s="14"/>
@@ -2964,12 +2946,12 @@
     <row r="66" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="13"/>
       <c r="C66" s="14"/>
-      <c r="D66" s="137" t="s">
+      <c r="D66" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="E66" s="137"/>
-      <c r="F66" s="137"/>
-      <c r="G66" s="137"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
       <c r="H66" s="16"/>
       <c r="I66" s="16"/>
       <c r="J66" s="17"/>
@@ -2982,15 +2964,17 @@
     <row r="67" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="13"/>
       <c r="C67" s="14"/>
-      <c r="D67" s="136"/>
-      <c r="E67" s="136"/>
-      <c r="F67" s="136"/>
-      <c r="G67" s="136"/>
-      <c r="H67" s="136"/>
-      <c r="I67" s="136"/>
-      <c r="J67" s="136"/>
-      <c r="K67" s="136"/>
-      <c r="L67" s="136"/>
+      <c r="D67" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="35"/>
+      <c r="K67" s="35"/>
+      <c r="L67" s="35"/>
       <c r="M67" s="14"/>
       <c r="N67" s="14"/>
       <c r="O67" s="14"/>
@@ -2998,15 +2982,15 @@
     <row r="68" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="13"/>
       <c r="C68" s="14"/>
-      <c r="D68" s="136"/>
-      <c r="E68" s="136"/>
-      <c r="F68" s="136"/>
-      <c r="G68" s="136"/>
-      <c r="H68" s="136"/>
-      <c r="I68" s="136"/>
-      <c r="J68" s="136"/>
-      <c r="K68" s="136"/>
-      <c r="L68" s="136"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
+      <c r="L68" s="35"/>
       <c r="M68" s="14"/>
       <c r="N68" s="14"/>
       <c r="O68" s="14"/>
@@ -3014,12 +2998,12 @@
     <row r="69" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="13"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="137" t="s">
+      <c r="D69" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="E69" s="137"/>
-      <c r="F69" s="137"/>
-      <c r="G69" s="137"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
       <c r="H69" s="16"/>
       <c r="I69" s="16"/>
       <c r="J69" s="17"/>
@@ -3032,15 +3016,15 @@
     <row r="70" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="13"/>
       <c r="C70" s="14"/>
-      <c r="D70" s="136"/>
-      <c r="E70" s="136"/>
-      <c r="F70" s="136"/>
-      <c r="G70" s="136"/>
-      <c r="H70" s="136"/>
-      <c r="I70" s="136"/>
-      <c r="J70" s="136"/>
-      <c r="K70" s="136"/>
-      <c r="L70" s="136"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="35"/>
+      <c r="K70" s="35"/>
+      <c r="L70" s="35"/>
       <c r="M70" s="14"/>
       <c r="N70" s="14"/>
       <c r="O70" s="14"/>
@@ -3048,15 +3032,15 @@
     <row r="71" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="13"/>
       <c r="C71" s="14"/>
-      <c r="D71" s="136"/>
-      <c r="E71" s="136"/>
-      <c r="F71" s="136"/>
-      <c r="G71" s="136"/>
-      <c r="H71" s="136"/>
-      <c r="I71" s="136"/>
-      <c r="J71" s="136"/>
-      <c r="K71" s="136"/>
-      <c r="L71" s="136"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="35"/>
+      <c r="F71" s="35"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="35"/>
+      <c r="I71" s="35"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
+      <c r="L71" s="35"/>
       <c r="M71" s="14"/>
       <c r="N71" s="14"/>
       <c r="O71" s="14"/>
@@ -3064,12 +3048,12 @@
     <row r="72" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="13"/>
       <c r="C72" s="14"/>
-      <c r="D72" s="137" t="s">
+      <c r="D72" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="E72" s="137"/>
-      <c r="F72" s="137"/>
-      <c r="G72" s="137"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
       <c r="H72" s="16"/>
       <c r="I72" s="16"/>
       <c r="J72" s="17"/>
@@ -3082,15 +3066,15 @@
     <row r="73" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="13"/>
       <c r="C73" s="14"/>
-      <c r="D73" s="136"/>
-      <c r="E73" s="136"/>
-      <c r="F73" s="136"/>
-      <c r="G73" s="136"/>
-      <c r="H73" s="136"/>
-      <c r="I73" s="136"/>
-      <c r="J73" s="136"/>
-      <c r="K73" s="136"/>
-      <c r="L73" s="136"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="35"/>
+      <c r="I73" s="35"/>
+      <c r="J73" s="35"/>
+      <c r="K73" s="35"/>
+      <c r="L73" s="35"/>
       <c r="M73" s="14"/>
       <c r="N73" s="14"/>
       <c r="O73" s="14"/>
@@ -3098,15 +3082,15 @@
     <row r="74" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="13"/>
       <c r="C74" s="14"/>
-      <c r="D74" s="136"/>
-      <c r="E74" s="136"/>
-      <c r="F74" s="136"/>
-      <c r="G74" s="136"/>
-      <c r="H74" s="136"/>
-      <c r="I74" s="136"/>
-      <c r="J74" s="136"/>
-      <c r="K74" s="136"/>
-      <c r="L74" s="136"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="35"/>
+      <c r="I74" s="35"/>
+      <c r="J74" s="35"/>
+      <c r="K74" s="35"/>
+      <c r="L74" s="35"/>
       <c r="M74" s="14"/>
       <c r="N74" s="14"/>
       <c r="O74" s="14"/>
@@ -3129,101 +3113,101 @@
     </row>
     <row r="76" spans="2:15" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="13"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="27"/>
-      <c r="I76" s="29"/>
-      <c r="J76" s="29"/>
-      <c r="K76" s="27"/>
-      <c r="L76" s="27"/>
-      <c r="M76" s="29"/>
-      <c r="N76" s="29"/>
-      <c r="O76" s="29"/>
+      <c r="C76" s="142"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="142"/>
+      <c r="G76" s="140"/>
+      <c r="H76" s="140"/>
+      <c r="I76" s="142"/>
+      <c r="J76" s="142"/>
+      <c r="K76" s="140"/>
+      <c r="L76" s="140"/>
+      <c r="M76" s="142"/>
+      <c r="N76" s="142"/>
+      <c r="O76" s="142"/>
     </row>
     <row r="77" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="13"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="27"/>
-      <c r="H77" s="27"/>
-      <c r="I77" s="29"/>
-      <c r="J77" s="29"/>
-      <c r="K77" s="27"/>
-      <c r="L77" s="27"/>
-      <c r="M77" s="29"/>
-      <c r="N77" s="29"/>
-      <c r="O77" s="29"/>
+      <c r="C77" s="142"/>
+      <c r="D77" s="142"/>
+      <c r="E77" s="142"/>
+      <c r="F77" s="142"/>
+      <c r="G77" s="140"/>
+      <c r="H77" s="140"/>
+      <c r="I77" s="142"/>
+      <c r="J77" s="142"/>
+      <c r="K77" s="140"/>
+      <c r="L77" s="140"/>
+      <c r="M77" s="142"/>
+      <c r="N77" s="142"/>
+      <c r="O77" s="142"/>
     </row>
     <row r="78" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="13"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
-      <c r="F78" s="29"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="29"/>
-      <c r="J78" s="29"/>
-      <c r="K78" s="27"/>
-      <c r="L78" s="27"/>
-      <c r="M78" s="29"/>
-      <c r="N78" s="29"/>
-      <c r="O78" s="29"/>
+      <c r="C78" s="142"/>
+      <c r="D78" s="142"/>
+      <c r="E78" s="142"/>
+      <c r="F78" s="142"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="140"/>
+      <c r="I78" s="142"/>
+      <c r="J78" s="142"/>
+      <c r="K78" s="140"/>
+      <c r="L78" s="140"/>
+      <c r="M78" s="142"/>
+      <c r="N78" s="142"/>
+      <c r="O78" s="142"/>
     </row>
     <row r="79" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="13"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
-      <c r="F79" s="29"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="29"/>
-      <c r="J79" s="29"/>
-      <c r="K79" s="27"/>
-      <c r="L79" s="27"/>
-      <c r="M79" s="29"/>
-      <c r="N79" s="29"/>
-      <c r="O79" s="29"/>
+      <c r="C79" s="142"/>
+      <c r="D79" s="142"/>
+      <c r="E79" s="142"/>
+      <c r="F79" s="142"/>
+      <c r="G79" s="140"/>
+      <c r="H79" s="140"/>
+      <c r="I79" s="142"/>
+      <c r="J79" s="142"/>
+      <c r="K79" s="140"/>
+      <c r="L79" s="140"/>
+      <c r="M79" s="142"/>
+      <c r="N79" s="142"/>
+      <c r="O79" s="142"/>
     </row>
     <row r="80" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="13"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="30"/>
-      <c r="J80" s="30"/>
-      <c r="K80" s="27"/>
-      <c r="L80" s="27"/>
-      <c r="M80" s="30"/>
-      <c r="N80" s="30"/>
-      <c r="O80" s="30"/>
+      <c r="C80" s="143"/>
+      <c r="D80" s="143"/>
+      <c r="E80" s="143"/>
+      <c r="F80" s="143"/>
+      <c r="G80" s="140"/>
+      <c r="H80" s="140"/>
+      <c r="I80" s="143"/>
+      <c r="J80" s="143"/>
+      <c r="K80" s="140"/>
+      <c r="L80" s="140"/>
+      <c r="M80" s="143"/>
+      <c r="N80" s="143"/>
+      <c r="O80" s="143"/>
     </row>
     <row r="81" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="13"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
-      <c r="F81" s="26"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="28" t="s">
+      <c r="C81" s="139"/>
+      <c r="D81" s="139"/>
+      <c r="E81" s="139"/>
+      <c r="F81" s="139"/>
+      <c r="G81" s="140"/>
+      <c r="H81" s="140"/>
+      <c r="I81" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="J81" s="28"/>
-      <c r="K81" s="27"/>
-      <c r="L81" s="27"/>
-      <c r="M81" s="26"/>
-      <c r="N81" s="26"/>
-      <c r="O81" s="26"/>
+      <c r="J81" s="141"/>
+      <c r="K81" s="140"/>
+      <c r="L81" s="140"/>
+      <c r="M81" s="139"/>
+      <c r="N81" s="139"/>
+      <c r="O81" s="139"/>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="13"/>
@@ -3243,29 +3227,175 @@
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="13"/>
-      <c r="C83" s="158"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="20"/>
-      <c r="K83" s="20"/>
-      <c r="L83" s="20"/>
-      <c r="M83" s="158"/>
-      <c r="N83" s="158"/>
-      <c r="O83" s="158"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="34"/>
+      <c r="I83" s="34"/>
+      <c r="J83" s="34"/>
+      <c r="K83" s="34"/>
+      <c r="L83" s="34"/>
+      <c r="M83" s="21"/>
+      <c r="N83" s="21"/>
+      <c r="O83" s="21"/>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B84" s="13"/>
-      <c r="H84" s="18" t="s">
+      <c r="H84" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I84" s="18"/>
+      <c r="I84" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="170">
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="C38:O40"/>
+    <mergeCell ref="K10:O10"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="M81:O81"/>
+    <mergeCell ref="C76:F80"/>
+    <mergeCell ref="G76:H80"/>
+    <mergeCell ref="I76:J80"/>
+    <mergeCell ref="K76:L80"/>
+    <mergeCell ref="M76:O80"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="F44:L44"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="E9:O9"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="G14:O14"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="G15:O15"/>
+    <mergeCell ref="G16:O16"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:O32"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G29:O29"/>
+    <mergeCell ref="G30:O30"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G23:O23"/>
+    <mergeCell ref="G24:O24"/>
+    <mergeCell ref="G25:O25"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G35:O35"/>
+    <mergeCell ref="G36:O36"/>
+    <mergeCell ref="G37:O37"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G33:O33"/>
+    <mergeCell ref="G34:O34"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G17:O17"/>
+    <mergeCell ref="G18:O18"/>
+    <mergeCell ref="G19:O19"/>
+    <mergeCell ref="G31:O31"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G26:O26"/>
+    <mergeCell ref="G27:O27"/>
+    <mergeCell ref="G28:O28"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="C14:C22"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G20:O20"/>
+    <mergeCell ref="G21:O21"/>
+    <mergeCell ref="G22:O22"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="D58:E59"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J58:L59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="D57:L57"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J47:L48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="J51:L51"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="J62:L62"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="D2:M2"/>
     <mergeCell ref="D3:M3"/>
@@ -3290,171 +3420,25 @@
     <mergeCell ref="D55:E55"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="H55:I55"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="J47:L48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="D58:E59"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="J58:L59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="D57:L57"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="J51:L51"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="C14:C22"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G20:O20"/>
-    <mergeCell ref="G21:O21"/>
-    <mergeCell ref="G22:O22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G17:O17"/>
-    <mergeCell ref="G18:O18"/>
-    <mergeCell ref="G19:O19"/>
-    <mergeCell ref="G31:O31"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G26:O26"/>
-    <mergeCell ref="G27:O27"/>
-    <mergeCell ref="G28:O28"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G23:O23"/>
-    <mergeCell ref="G24:O24"/>
-    <mergeCell ref="G25:O25"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G35:O35"/>
-    <mergeCell ref="G36:O36"/>
-    <mergeCell ref="G37:O37"/>
-    <mergeCell ref="E9:O9"/>
-    <mergeCell ref="C8:O8"/>
-    <mergeCell ref="G14:O14"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="G15:O15"/>
-    <mergeCell ref="G16:O16"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G32:O32"/>
-    <mergeCell ref="G33:O33"/>
-    <mergeCell ref="G34:O34"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G29:O29"/>
-    <mergeCell ref="G30:O30"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="C38:O40"/>
-    <mergeCell ref="K10:O10"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="C81:F81"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="M81:O81"/>
-    <mergeCell ref="C76:F80"/>
-    <mergeCell ref="G76:H80"/>
-    <mergeCell ref="I76:J80"/>
-    <mergeCell ref="K76:L80"/>
-    <mergeCell ref="M76:O80"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="F44:L44"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="D35:F35"/>
   </mergeCells>
+  <conditionalFormatting sqref="D83:L83">
+    <cfRule type="containsBlanks" dxfId="3" priority="1">
+      <formula>LEN(TRIM(D83))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F49:L56">
-    <cfRule type="containsBlanks" dxfId="6" priority="3">
+    <cfRule type="containsBlanks" dxfId="2" priority="3">
       <formula>LEN(TRIM(F49))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60:L64">
-    <cfRule type="containsBlanks" dxfId="5" priority="2">
+    <cfRule type="containsBlanks" dxfId="1" priority="2">
       <formula>LEN(TRIM(F60))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10:O10 E11:J11 M11:O11 L13:O13 G14:O22 G26:O37 F42:G42 J42:L42 F43 D67:L68 D70:L71 D73:L74 C81:F81 M81:O81">
-    <cfRule type="containsBlanks" dxfId="4" priority="4">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
       <formula>LEN(TRIM(C10))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D83:L83">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(D83))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="756" yWindow="874" count="46">

--- a/Formatos/Visita Extraordinaria GFPI-F023.xlsx
+++ b/Formatos/Visita Extraordinaria GFPI-F023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/834af06e427efe68/Documents/Seto 2026/sena/Manual SENA Etapa Productiva/manual-aprendiz-sena/Formatos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363F5DF6-A38B-4E41-A740-E7B496CB2FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{BE778CA7-250F-4550-B2A8-B238D2344594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39A8E1DC-D01E-47AE-8BC8-37253ECF1F7A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
   <si>
     <t>Información general</t>
   </si>
@@ -334,9 +334,6 @@
   </si>
   <si>
     <t>virtual</t>
-  </si>
-  <si>
-    <t>.</t>
   </si>
 </sst>
 </file>
@@ -902,6 +899,435 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -909,6 +1335,9 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -916,474 +1345,49 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDD5555"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1408,7 +1412,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDD5555"/>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1789,804 +1807,804 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="138" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="24"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="140"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="142"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="143" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="30"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="145"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="27"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="142"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="30"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="145"/>
     </row>
     <row r="6" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="18" t="b">
+      <c r="E6" s="147"/>
+      <c r="F6" s="148" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="149" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="18" t="b">
+      <c r="H6" s="147"/>
+      <c r="I6" s="147"/>
+      <c r="J6" s="148" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="33" t="s">
+      <c r="K6" s="149" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="19" t="b">
+      <c r="L6" s="147"/>
+      <c r="M6" s="150" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="13"/>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="120"/>
-      <c r="K8" s="120"/>
-      <c r="L8" s="120"/>
-      <c r="M8" s="120"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="120"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
     </row>
     <row r="9" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="13"/>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="89"/>
-      <c r="E9" s="106" t="s">
+      <c r="D9" s="48"/>
+      <c r="E9" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="107"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="54"/>
     </row>
     <row r="10" spans="2:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="13"/>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="89"/>
-      <c r="E10" s="90" t="s">
+      <c r="D10" s="48"/>
+      <c r="E10" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="92"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="90"/>
       <c r="J10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="85"/>
-      <c r="L10" s="86"/>
-      <c r="M10" s="86"/>
-      <c r="N10" s="86"/>
-      <c r="O10" s="87"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="23"/>
     </row>
     <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="13"/>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="89"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="55" t="s">
+      <c r="D11" s="48"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="123"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="62"/>
     </row>
     <row r="12" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="13"/>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="89"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="106" t="s">
+      <c r="F12" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="107"/>
-      <c r="H12" s="57" t="s">
+      <c r="G12" s="54"/>
+      <c r="H12" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="59"/>
+      <c r="I12" s="104"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="57" t="s">
+      <c r="K12" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="59"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="126"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65"/>
     </row>
     <row r="13" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13"/>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="89"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="93" t="s">
+      <c r="D13" s="48"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="94"/>
-      <c r="K13" s="95"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="129"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="151"/>
+      <c r="M13" s="152"/>
+      <c r="N13" s="152"/>
+      <c r="O13" s="153"/>
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13"/>
-      <c r="C14" s="96" t="s">
+      <c r="C14" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="99"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="112"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="113"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="59"/>
     </row>
     <row r="15" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="100" t="s">
+      <c r="C15" s="73"/>
+      <c r="D15" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="101"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="131"/>
-      <c r="J15" s="131"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="131"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="132"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="68"/>
     </row>
     <row r="16" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="88" t="s">
+      <c r="C16" s="73"/>
+      <c r="D16" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="99"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="113"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="59"/>
     </row>
     <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="13"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="88" t="s">
+      <c r="C17" s="73"/>
+      <c r="D17" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="99"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
-      <c r="L17" s="112"/>
-      <c r="M17" s="112"/>
-      <c r="N17" s="112"/>
-      <c r="O17" s="113"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="59"/>
     </row>
     <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="88" t="s">
+      <c r="C18" s="73"/>
+      <c r="D18" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="99"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="112"/>
-      <c r="O18" s="113"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="59"/>
     </row>
     <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="13"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="88" t="s">
+      <c r="C19" s="73"/>
+      <c r="D19" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="113"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="59"/>
     </row>
     <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="13"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="88" t="s">
+      <c r="C20" s="73"/>
+      <c r="D20" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="99"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="110"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="51"/>
     </row>
     <row r="21" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="13"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="88" t="s">
+      <c r="C21" s="73"/>
+      <c r="D21" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="99"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="110"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="51"/>
     </row>
     <row r="22" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="13"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="88" t="s">
+      <c r="C22" s="74"/>
+      <c r="D22" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="99"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="109"/>
-      <c r="O22" s="110"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="51"/>
     </row>
     <row r="23" spans="2:15" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="13"/>
-      <c r="C23" s="114" t="s">
+      <c r="C23" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="88" t="s">
+      <c r="D23" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="99"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="115" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="116"/>
-      <c r="I23" s="116"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="116"/>
-      <c r="M23" s="116"/>
-      <c r="N23" s="116"/>
-      <c r="O23" s="117"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="77"/>
     </row>
     <row r="24" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="13"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="88" t="s">
+      <c r="C24" s="73"/>
+      <c r="D24" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="99"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="77"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="80"/>
     </row>
     <row r="25" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="13"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="88" t="s">
+      <c r="C25" s="74"/>
+      <c r="D25" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="99"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="115" t="s">
+      <c r="E25" s="47"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="H25" s="116"/>
-      <c r="I25" s="116"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="116"/>
-      <c r="M25" s="116"/>
-      <c r="N25" s="116"/>
-      <c r="O25" s="117"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="76"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="76"/>
+      <c r="M25" s="76"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="77"/>
     </row>
     <row r="26" spans="2:15" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="13"/>
       <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="88" t="s">
+      <c r="D26" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="99"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
-      <c r="O26" s="113"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="59"/>
     </row>
     <row r="27" spans="2:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="13"/>
       <c r="C27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="88" t="s">
+      <c r="D27" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="99"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="112"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="112"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="112"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="113"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="59"/>
     </row>
     <row r="28" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="13"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="88" t="s">
+      <c r="D28" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="99"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="112"/>
-      <c r="I28" s="112"/>
-      <c r="J28" s="112"/>
-      <c r="K28" s="112"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="112"/>
-      <c r="N28" s="112"/>
-      <c r="O28" s="113"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="59"/>
     </row>
     <row r="29" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="13"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="88" t="s">
+      <c r="D29" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="99"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="112"/>
-      <c r="I29" s="112"/>
-      <c r="J29" s="112"/>
-      <c r="K29" s="112"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="113"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="59"/>
     </row>
     <row r="30" spans="2:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="13"/>
       <c r="C30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="88" t="s">
+      <c r="D30" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="99"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="112"/>
-      <c r="I30" s="112"/>
-      <c r="J30" s="112"/>
-      <c r="K30" s="112"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
-      <c r="O30" s="113"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="59"/>
     </row>
     <row r="31" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="13"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="88" t="s">
+      <c r="D31" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="99"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="113"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="59"/>
     </row>
     <row r="32" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="13"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="88" t="s">
+      <c r="D32" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="99"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="109"/>
-      <c r="I32" s="109"/>
-      <c r="J32" s="109"/>
-      <c r="K32" s="109"/>
-      <c r="L32" s="109"/>
-      <c r="M32" s="109"/>
-      <c r="N32" s="109"/>
-      <c r="O32" s="110"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="51"/>
     </row>
     <row r="33" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="13"/>
       <c r="C33" s="6"/>
-      <c r="D33" s="88" t="s">
+      <c r="D33" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="99"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="111"/>
-      <c r="H33" s="112"/>
-      <c r="I33" s="112"/>
-      <c r="J33" s="112"/>
-      <c r="K33" s="112"/>
-      <c r="L33" s="112"/>
-      <c r="M33" s="112"/>
-      <c r="N33" s="112"/>
-      <c r="O33" s="113"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="59"/>
     </row>
     <row r="34" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="13"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="133" t="s">
+      <c r="D34" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="134"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="110"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="50"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="51"/>
     </row>
     <row r="35" spans="2:15" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="13"/>
       <c r="C35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="156" t="s">
+      <c r="D35" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="E35" s="157"/>
-      <c r="F35" s="158"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="109"/>
-      <c r="J35" s="109"/>
-      <c r="K35" s="109"/>
-      <c r="L35" s="109"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="109"/>
-      <c r="O35" s="110"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="51"/>
     </row>
     <row r="36" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="13"/>
       <c r="C36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="88" t="s">
+      <c r="D36" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="99"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="109"/>
-      <c r="I36" s="109"/>
-      <c r="J36" s="109"/>
-      <c r="K36" s="109"/>
-      <c r="L36" s="109"/>
-      <c r="M36" s="109"/>
-      <c r="N36" s="109"/>
-      <c r="O36" s="110"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="51"/>
     </row>
     <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="13"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="88" t="s">
+      <c r="D37" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="99"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="109"/>
-      <c r="I37" s="109"/>
-      <c r="J37" s="109"/>
-      <c r="K37" s="109"/>
-      <c r="L37" s="109"/>
-      <c r="M37" s="109"/>
-      <c r="N37" s="109"/>
-      <c r="O37" s="110"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="50"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="51"/>
     </row>
     <row r="38" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="13"/>
-      <c r="C38" s="136" t="s">
+      <c r="C38" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="136"/>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="136"/>
-      <c r="L38" s="136"/>
-      <c r="M38" s="136"/>
-      <c r="N38" s="136"/>
-      <c r="O38" s="136"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
     </row>
     <row r="39" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
-      <c r="C39" s="136"/>
-      <c r="D39" s="136"/>
-      <c r="E39" s="136"/>
-      <c r="F39" s="136"/>
-      <c r="G39" s="136"/>
-      <c r="H39" s="136"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="136"/>
-      <c r="L39" s="136"/>
-      <c r="M39" s="136"/>
-      <c r="N39" s="136"/>
-      <c r="O39" s="136"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
     </row>
     <row r="40" spans="2:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="13"/>
-      <c r="C40" s="136"/>
-      <c r="D40" s="136"/>
-      <c r="E40" s="136"/>
-      <c r="F40" s="136"/>
-      <c r="G40" s="136"/>
-      <c r="H40" s="136"/>
-      <c r="I40" s="136"/>
-      <c r="J40" s="136"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="136"/>
-      <c r="M40" s="136"/>
-      <c r="N40" s="136"/>
-      <c r="O40" s="136"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
     </row>
     <row r="41" spans="2:15" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="13"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="68" t="s">
+      <c r="D41" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
+      <c r="E41" s="123"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="123"/>
+      <c r="J41" s="123"/>
+      <c r="K41" s="123"/>
+      <c r="L41" s="123"/>
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
       <c r="O41" s="11"/>
     </row>
     <row r="42" spans="2:15" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="144" t="s">
+      <c r="D42" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="145"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="146" t="s">
+      <c r="E42" s="32"/>
+      <c r="F42" s="154"/>
+      <c r="G42" s="156"/>
+      <c r="H42" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="I42" s="147"/>
-      <c r="J42" s="72"/>
-      <c r="K42" s="73"/>
-      <c r="L42" s="74"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="154"/>
+      <c r="K42" s="155"/>
+      <c r="L42" s="156"/>
     </row>
     <row r="43" spans="2:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="144" t="s">
+      <c r="D43" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E43" s="145"/>
-      <c r="F43" s="20" t="s">
+      <c r="E43" s="32"/>
+      <c r="F43" s="157" t="s">
         <v>82</v>
       </c>
-      <c r="G43" s="148" t="s">
+      <c r="G43" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H43" s="149"/>
-      <c r="I43" s="147"/>
-      <c r="J43" s="153"/>
-      <c r="K43" s="154"/>
-      <c r="L43" s="155"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="34"/>
     </row>
     <row r="44" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="144" t="s">
+      <c r="D44" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="145"/>
-      <c r="F44" s="150"/>
-      <c r="G44" s="151"/>
-      <c r="H44" s="151"/>
-      <c r="I44" s="151"/>
-      <c r="J44" s="151"/>
-      <c r="K44" s="151"/>
-      <c r="L44" s="152"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="40"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="41"/>
     </row>
     <row r="45" spans="2:15" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="13"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="69" t="s">
+      <c r="D46" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="70"/>
-      <c r="K46" s="70"/>
-      <c r="L46" s="71"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="125"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="125"/>
+      <c r="J46" s="125"/>
+      <c r="K46" s="125"/>
+      <c r="L46" s="126"/>
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
       <c r="O46" s="11"/>
@@ -2594,21 +2612,21 @@
     <row r="47" spans="2:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="13"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="53" t="s">
+      <c r="D47" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="E47" s="54"/>
-      <c r="F47" s="57" t="s">
+      <c r="E47" s="119"/>
+      <c r="F47" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="60" t="s">
+      <c r="G47" s="120"/>
+      <c r="H47" s="120"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="K47" s="61"/>
-      <c r="L47" s="62"/>
+      <c r="K47" s="109"/>
+      <c r="L47" s="106"/>
       <c r="M47" s="11"/>
       <c r="N47" s="11"/>
       <c r="O47" s="11"/>
@@ -2616,19 +2634,19 @@
     <row r="48" spans="2:15" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="13"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="66" t="s">
+      <c r="D48" s="101"/>
+      <c r="E48" s="102"/>
+      <c r="F48" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="G48" s="67"/>
-      <c r="H48" s="66" t="s">
+      <c r="G48" s="122"/>
+      <c r="H48" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="I48" s="67"/>
-      <c r="J48" s="63"/>
-      <c r="K48" s="64"/>
-      <c r="L48" s="65"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="107"/>
+      <c r="K48" s="110"/>
+      <c r="L48" s="108"/>
       <c r="M48" s="11"/>
       <c r="N48" s="11"/>
       <c r="O48" s="11"/>
@@ -2636,17 +2654,17 @@
     <row r="49" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="13"/>
       <c r="C49" s="14"/>
-      <c r="D49" s="36" t="s">
+      <c r="D49" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="37"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="39"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="39"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="42"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="87"/>
+      <c r="H49" s="86"/>
+      <c r="I49" s="87"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="82"/>
+      <c r="L49" s="83"/>
       <c r="M49" s="14"/>
       <c r="N49" s="14"/>
       <c r="O49" s="14"/>
@@ -2654,17 +2672,17 @@
     <row r="50" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="13"/>
       <c r="C50" s="14"/>
-      <c r="D50" s="36" t="s">
+      <c r="D50" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="E50" s="37"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="39"/>
-      <c r="H50" s="137"/>
-      <c r="I50" s="138"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="42"/>
+      <c r="E50" s="85"/>
+      <c r="F50" s="86"/>
+      <c r="G50" s="87"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="82"/>
+      <c r="L50" s="83"/>
       <c r="M50" s="14"/>
       <c r="N50" s="14"/>
       <c r="O50" s="14"/>
@@ -2672,17 +2690,17 @@
     <row r="51" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="13"/>
       <c r="C51" s="14"/>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="42"/>
+      <c r="E51" s="85"/>
+      <c r="F51" s="86"/>
+      <c r="G51" s="87"/>
+      <c r="H51" s="86"/>
+      <c r="I51" s="87"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="82"/>
+      <c r="L51" s="83"/>
       <c r="M51" s="14"/>
       <c r="N51" s="14"/>
       <c r="O51" s="14"/>
@@ -2690,17 +2708,17 @@
     <row r="52" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="13"/>
       <c r="C52" s="14"/>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="E52" s="45"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="84"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="84"/>
-      <c r="J52" s="85"/>
-      <c r="K52" s="86"/>
-      <c r="L52" s="87"/>
+      <c r="E52" s="128"/>
+      <c r="F52" s="116"/>
+      <c r="G52" s="117"/>
+      <c r="H52" s="116"/>
+      <c r="I52" s="117"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="23"/>
       <c r="M52" s="14"/>
       <c r="N52" s="14"/>
       <c r="O52" s="14"/>
@@ -2708,17 +2726,17 @@
     <row r="53" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="13"/>
       <c r="C53" s="14"/>
-      <c r="D53" s="36" t="s">
+      <c r="D53" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="E53" s="37"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="42"/>
+      <c r="E53" s="85"/>
+      <c r="F53" s="86"/>
+      <c r="G53" s="87"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="87"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="82"/>
+      <c r="L53" s="83"/>
       <c r="M53" s="14"/>
       <c r="N53" s="14"/>
       <c r="O53" s="14"/>
@@ -2726,17 +2744,17 @@
     <row r="54" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="13"/>
       <c r="C54" s="14"/>
-      <c r="D54" s="36" t="s">
+      <c r="D54" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="E54" s="37"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="42"/>
+      <c r="E54" s="85"/>
+      <c r="F54" s="86"/>
+      <c r="G54" s="87"/>
+      <c r="H54" s="86"/>
+      <c r="I54" s="87"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="83"/>
       <c r="M54" s="14"/>
       <c r="N54" s="14"/>
       <c r="O54" s="14"/>
@@ -2744,17 +2762,17 @@
     <row r="55" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="13"/>
       <c r="C55" s="14"/>
-      <c r="D55" s="36" t="s">
+      <c r="D55" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="E55" s="37"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="42"/>
+      <c r="E55" s="85"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="87"/>
+      <c r="H55" s="86"/>
+      <c r="I55" s="87"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="82"/>
+      <c r="L55" s="83"/>
       <c r="M55" s="14"/>
       <c r="N55" s="14"/>
       <c r="O55" s="14"/>
@@ -2762,17 +2780,17 @@
     <row r="56" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="13"/>
       <c r="C56" s="14"/>
-      <c r="D56" s="46" t="s">
+      <c r="D56" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="E56" s="47"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="51"/>
-      <c r="L56" s="52"/>
+      <c r="E56" s="130"/>
+      <c r="F56" s="131"/>
+      <c r="G56" s="132"/>
+      <c r="H56" s="131"/>
+      <c r="I56" s="132"/>
+      <c r="J56" s="133"/>
+      <c r="K56" s="134"/>
+      <c r="L56" s="135"/>
       <c r="M56" s="14"/>
       <c r="N56" s="14"/>
       <c r="O56" s="14"/>
@@ -2780,17 +2798,17 @@
     <row r="57" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="13"/>
       <c r="C57" s="14"/>
-      <c r="D57" s="80" t="s">
+      <c r="D57" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="E57" s="81"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="82"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="114"/>
+      <c r="H57" s="114"/>
+      <c r="I57" s="114"/>
+      <c r="J57" s="114"/>
+      <c r="K57" s="114"/>
+      <c r="L57" s="115"/>
       <c r="M57" s="14"/>
       <c r="N57" s="14"/>
       <c r="O57" s="14"/>
@@ -2798,21 +2816,21 @@
     <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="13"/>
       <c r="C58" s="14"/>
-      <c r="D58" s="60" t="s">
+      <c r="D58" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="E58" s="62"/>
-      <c r="F58" s="75" t="s">
+      <c r="E58" s="106"/>
+      <c r="F58" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="G58" s="76"/>
-      <c r="H58" s="76"/>
-      <c r="I58" s="77"/>
-      <c r="J58" s="60" t="s">
+      <c r="G58" s="79"/>
+      <c r="H58" s="79"/>
+      <c r="I58" s="80"/>
+      <c r="J58" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="K58" s="61"/>
-      <c r="L58" s="62"/>
+      <c r="K58" s="109"/>
+      <c r="L58" s="106"/>
       <c r="M58" s="14"/>
       <c r="N58" s="14"/>
       <c r="O58" s="14"/>
@@ -2820,19 +2838,19 @@
     <row r="59" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="13"/>
       <c r="C59" s="14"/>
-      <c r="D59" s="63"/>
-      <c r="E59" s="65"/>
-      <c r="F59" s="78" t="s">
+      <c r="D59" s="107"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="G59" s="79"/>
-      <c r="H59" s="78" t="s">
+      <c r="G59" s="112"/>
+      <c r="H59" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="I59" s="79"/>
-      <c r="J59" s="63"/>
-      <c r="K59" s="64"/>
-      <c r="L59" s="65"/>
+      <c r="I59" s="112"/>
+      <c r="J59" s="107"/>
+      <c r="K59" s="110"/>
+      <c r="L59" s="108"/>
       <c r="M59" s="14"/>
       <c r="N59" s="14"/>
       <c r="O59" s="14"/>
@@ -2840,17 +2858,17 @@
     <row r="60" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="13"/>
       <c r="C60" s="14"/>
-      <c r="D60" s="36" t="s">
+      <c r="D60" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="E60" s="37"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="41"/>
-      <c r="L60" s="42"/>
+      <c r="E60" s="85"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="87"/>
+      <c r="H60" s="86"/>
+      <c r="I60" s="87"/>
+      <c r="J60" s="81"/>
+      <c r="K60" s="82"/>
+      <c r="L60" s="83"/>
       <c r="M60" s="14"/>
       <c r="N60" s="14"/>
       <c r="O60" s="14"/>
@@ -2858,17 +2876,17 @@
     <row r="61" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="13"/>
       <c r="C61" s="14"/>
-      <c r="D61" s="36" t="s">
+      <c r="D61" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="37"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="40"/>
-      <c r="K61" s="41"/>
-      <c r="L61" s="42"/>
+      <c r="E61" s="85"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="87"/>
+      <c r="H61" s="86"/>
+      <c r="I61" s="87"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="82"/>
+      <c r="L61" s="83"/>
       <c r="M61" s="14"/>
       <c r="N61" s="14"/>
       <c r="O61" s="14"/>
@@ -2876,17 +2894,17 @@
     <row r="62" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="13"/>
       <c r="C62" s="14"/>
-      <c r="D62" s="36" t="s">
+      <c r="D62" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="E62" s="37"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="40"/>
-      <c r="K62" s="41"/>
-      <c r="L62" s="42"/>
+      <c r="E62" s="85"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="87"/>
+      <c r="H62" s="86"/>
+      <c r="I62" s="87"/>
+      <c r="J62" s="81"/>
+      <c r="K62" s="82"/>
+      <c r="L62" s="83"/>
       <c r="M62" s="14"/>
       <c r="N62" s="14"/>
       <c r="O62" s="14"/>
@@ -2894,17 +2912,17 @@
     <row r="63" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="13"/>
       <c r="C63" s="14"/>
-      <c r="D63" s="36" t="s">
+      <c r="D63" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="E63" s="37"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="39"/>
-      <c r="J63" s="40"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="42"/>
+      <c r="E63" s="85"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="87"/>
+      <c r="H63" s="86"/>
+      <c r="I63" s="87"/>
+      <c r="J63" s="81"/>
+      <c r="K63" s="82"/>
+      <c r="L63" s="83"/>
       <c r="M63" s="14"/>
       <c r="N63" s="14"/>
       <c r="O63" s="14"/>
@@ -2912,17 +2930,17 @@
     <row r="64" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="13"/>
       <c r="C64" s="14"/>
-      <c r="D64" s="36" t="s">
+      <c r="D64" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="E64" s="37"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="40"/>
-      <c r="K64" s="41"/>
-      <c r="L64" s="42"/>
+      <c r="E64" s="85"/>
+      <c r="F64" s="86"/>
+      <c r="G64" s="87"/>
+      <c r="H64" s="86"/>
+      <c r="I64" s="87"/>
+      <c r="J64" s="81"/>
+      <c r="K64" s="82"/>
+      <c r="L64" s="83"/>
       <c r="M64" s="14"/>
       <c r="N64" s="14"/>
       <c r="O64" s="14"/>
@@ -2946,12 +2964,12 @@
     <row r="66" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="13"/>
       <c r="C66" s="14"/>
-      <c r="D66" s="43" t="s">
+      <c r="D66" s="137" t="s">
         <v>71</v>
       </c>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="43"/>
+      <c r="E66" s="137"/>
+      <c r="F66" s="137"/>
+      <c r="G66" s="137"/>
       <c r="H66" s="16"/>
       <c r="I66" s="16"/>
       <c r="J66" s="17"/>
@@ -2964,17 +2982,15 @@
     <row r="67" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="13"/>
       <c r="C67" s="14"/>
-      <c r="D67" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="35"/>
-      <c r="L67" s="35"/>
+      <c r="D67" s="136"/>
+      <c r="E67" s="136"/>
+      <c r="F67" s="136"/>
+      <c r="G67" s="136"/>
+      <c r="H67" s="136"/>
+      <c r="I67" s="136"/>
+      <c r="J67" s="136"/>
+      <c r="K67" s="136"/>
+      <c r="L67" s="136"/>
       <c r="M67" s="14"/>
       <c r="N67" s="14"/>
       <c r="O67" s="14"/>
@@ -2982,15 +2998,15 @@
     <row r="68" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="13"/>
       <c r="C68" s="14"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="J68" s="35"/>
-      <c r="K68" s="35"/>
-      <c r="L68" s="35"/>
+      <c r="D68" s="136"/>
+      <c r="E68" s="136"/>
+      <c r="F68" s="136"/>
+      <c r="G68" s="136"/>
+      <c r="H68" s="136"/>
+      <c r="I68" s="136"/>
+      <c r="J68" s="136"/>
+      <c r="K68" s="136"/>
+      <c r="L68" s="136"/>
       <c r="M68" s="14"/>
       <c r="N68" s="14"/>
       <c r="O68" s="14"/>
@@ -2998,12 +3014,12 @@
     <row r="69" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="13"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="43" t="s">
+      <c r="D69" s="137" t="s">
         <v>72</v>
       </c>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="43"/>
+      <c r="E69" s="137"/>
+      <c r="F69" s="137"/>
+      <c r="G69" s="137"/>
       <c r="H69" s="16"/>
       <c r="I69" s="16"/>
       <c r="J69" s="17"/>
@@ -3016,15 +3032,15 @@
     <row r="70" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="13"/>
       <c r="C70" s="14"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="35"/>
-      <c r="L70" s="35"/>
+      <c r="D70" s="136"/>
+      <c r="E70" s="136"/>
+      <c r="F70" s="136"/>
+      <c r="G70" s="136"/>
+      <c r="H70" s="136"/>
+      <c r="I70" s="136"/>
+      <c r="J70" s="136"/>
+      <c r="K70" s="136"/>
+      <c r="L70" s="136"/>
       <c r="M70" s="14"/>
       <c r="N70" s="14"/>
       <c r="O70" s="14"/>
@@ -3032,15 +3048,15 @@
     <row r="71" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="13"/>
       <c r="C71" s="14"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="35"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
-      <c r="J71" s="35"/>
-      <c r="K71" s="35"/>
-      <c r="L71" s="35"/>
+      <c r="D71" s="136"/>
+      <c r="E71" s="136"/>
+      <c r="F71" s="136"/>
+      <c r="G71" s="136"/>
+      <c r="H71" s="136"/>
+      <c r="I71" s="136"/>
+      <c r="J71" s="136"/>
+      <c r="K71" s="136"/>
+      <c r="L71" s="136"/>
       <c r="M71" s="14"/>
       <c r="N71" s="14"/>
       <c r="O71" s="14"/>
@@ -3048,12 +3064,12 @@
     <row r="72" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="13"/>
       <c r="C72" s="14"/>
-      <c r="D72" s="43" t="s">
+      <c r="D72" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="43"/>
+      <c r="E72" s="137"/>
+      <c r="F72" s="137"/>
+      <c r="G72" s="137"/>
       <c r="H72" s="16"/>
       <c r="I72" s="16"/>
       <c r="J72" s="17"/>
@@ -3066,15 +3082,15 @@
     <row r="73" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="13"/>
       <c r="C73" s="14"/>
-      <c r="D73" s="35"/>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="35"/>
-      <c r="K73" s="35"/>
-      <c r="L73" s="35"/>
+      <c r="D73" s="136"/>
+      <c r="E73" s="136"/>
+      <c r="F73" s="136"/>
+      <c r="G73" s="136"/>
+      <c r="H73" s="136"/>
+      <c r="I73" s="136"/>
+      <c r="J73" s="136"/>
+      <c r="K73" s="136"/>
+      <c r="L73" s="136"/>
       <c r="M73" s="14"/>
       <c r="N73" s="14"/>
       <c r="O73" s="14"/>
@@ -3082,15 +3098,15 @@
     <row r="74" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="13"/>
       <c r="C74" s="14"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
-      <c r="J74" s="35"/>
-      <c r="K74" s="35"/>
-      <c r="L74" s="35"/>
+      <c r="D74" s="136"/>
+      <c r="E74" s="136"/>
+      <c r="F74" s="136"/>
+      <c r="G74" s="136"/>
+      <c r="H74" s="136"/>
+      <c r="I74" s="136"/>
+      <c r="J74" s="136"/>
+      <c r="K74" s="136"/>
+      <c r="L74" s="136"/>
       <c r="M74" s="14"/>
       <c r="N74" s="14"/>
       <c r="O74" s="14"/>
@@ -3113,101 +3129,101 @@
     </row>
     <row r="76" spans="2:15" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="13"/>
-      <c r="C76" s="142"/>
-      <c r="D76" s="142"/>
-      <c r="E76" s="142"/>
-      <c r="F76" s="142"/>
-      <c r="G76" s="140"/>
-      <c r="H76" s="140"/>
-      <c r="I76" s="142"/>
-      <c r="J76" s="142"/>
-      <c r="K76" s="140"/>
-      <c r="L76" s="140"/>
-      <c r="M76" s="142"/>
-      <c r="N76" s="142"/>
-      <c r="O76" s="142"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="27"/>
+      <c r="L76" s="27"/>
+      <c r="M76" s="29"/>
+      <c r="N76" s="29"/>
+      <c r="O76" s="29"/>
     </row>
     <row r="77" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="13"/>
-      <c r="C77" s="142"/>
-      <c r="D77" s="142"/>
-      <c r="E77" s="142"/>
-      <c r="F77" s="142"/>
-      <c r="G77" s="140"/>
-      <c r="H77" s="140"/>
-      <c r="I77" s="142"/>
-      <c r="J77" s="142"/>
-      <c r="K77" s="140"/>
-      <c r="L77" s="140"/>
-      <c r="M77" s="142"/>
-      <c r="N77" s="142"/>
-      <c r="O77" s="142"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="29"/>
+      <c r="K77" s="27"/>
+      <c r="L77" s="27"/>
+      <c r="M77" s="29"/>
+      <c r="N77" s="29"/>
+      <c r="O77" s="29"/>
     </row>
     <row r="78" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="13"/>
-      <c r="C78" s="142"/>
-      <c r="D78" s="142"/>
-      <c r="E78" s="142"/>
-      <c r="F78" s="142"/>
-      <c r="G78" s="140"/>
-      <c r="H78" s="140"/>
-      <c r="I78" s="142"/>
-      <c r="J78" s="142"/>
-      <c r="K78" s="140"/>
-      <c r="L78" s="140"/>
-      <c r="M78" s="142"/>
-      <c r="N78" s="142"/>
-      <c r="O78" s="142"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
+      <c r="E78" s="29"/>
+      <c r="F78" s="29"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
+      <c r="I78" s="29"/>
+      <c r="J78" s="29"/>
+      <c r="K78" s="27"/>
+      <c r="L78" s="27"/>
+      <c r="M78" s="29"/>
+      <c r="N78" s="29"/>
+      <c r="O78" s="29"/>
     </row>
     <row r="79" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="13"/>
-      <c r="C79" s="142"/>
-      <c r="D79" s="142"/>
-      <c r="E79" s="142"/>
-      <c r="F79" s="142"/>
-      <c r="G79" s="140"/>
-      <c r="H79" s="140"/>
-      <c r="I79" s="142"/>
-      <c r="J79" s="142"/>
-      <c r="K79" s="140"/>
-      <c r="L79" s="140"/>
-      <c r="M79" s="142"/>
-      <c r="N79" s="142"/>
-      <c r="O79" s="142"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="29"/>
+      <c r="E79" s="29"/>
+      <c r="F79" s="29"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="29"/>
+      <c r="J79" s="29"/>
+      <c r="K79" s="27"/>
+      <c r="L79" s="27"/>
+      <c r="M79" s="29"/>
+      <c r="N79" s="29"/>
+      <c r="O79" s="29"/>
     </row>
     <row r="80" spans="2:15" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="13"/>
-      <c r="C80" s="143"/>
-      <c r="D80" s="143"/>
-      <c r="E80" s="143"/>
-      <c r="F80" s="143"/>
-      <c r="G80" s="140"/>
-      <c r="H80" s="140"/>
-      <c r="I80" s="143"/>
-      <c r="J80" s="143"/>
-      <c r="K80" s="140"/>
-      <c r="L80" s="140"/>
-      <c r="M80" s="143"/>
-      <c r="N80" s="143"/>
-      <c r="O80" s="143"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="27"/>
+      <c r="L80" s="27"/>
+      <c r="M80" s="30"/>
+      <c r="N80" s="30"/>
+      <c r="O80" s="30"/>
     </row>
     <row r="81" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="13"/>
-      <c r="C81" s="139"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="139"/>
-      <c r="F81" s="139"/>
-      <c r="G81" s="140"/>
-      <c r="H81" s="140"/>
-      <c r="I81" s="141" t="s">
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="J81" s="141"/>
-      <c r="K81" s="140"/>
-      <c r="L81" s="140"/>
-      <c r="M81" s="139"/>
-      <c r="N81" s="139"/>
-      <c r="O81" s="139"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="27"/>
+      <c r="L81" s="27"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="13"/>
@@ -3227,95 +3243,109 @@
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="13"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="34"/>
-      <c r="F83" s="34"/>
-      <c r="G83" s="34"/>
-      <c r="H83" s="34"/>
-      <c r="I83" s="34"/>
-      <c r="J83" s="34"/>
-      <c r="K83" s="34"/>
-      <c r="L83" s="34"/>
-      <c r="M83" s="21"/>
-      <c r="N83" s="21"/>
-      <c r="O83" s="21"/>
+      <c r="C83" s="158"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="20"/>
+      <c r="L83" s="20"/>
+      <c r="M83" s="158"/>
+      <c r="N83" s="158"/>
+      <c r="O83" s="158"/>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B84" s="13"/>
-      <c r="H84" s="26" t="s">
+      <c r="H84" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="I84" s="26"/>
+      <c r="I84" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="170">
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="C38:O40"/>
-    <mergeCell ref="K10:O10"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="C81:F81"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="M81:O81"/>
-    <mergeCell ref="C76:F80"/>
-    <mergeCell ref="G76:H80"/>
-    <mergeCell ref="I76:J80"/>
-    <mergeCell ref="K76:L80"/>
-    <mergeCell ref="M76:O80"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="F44:L44"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="E9:O9"/>
-    <mergeCell ref="C8:O8"/>
-    <mergeCell ref="G14:O14"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="G15:O15"/>
-    <mergeCell ref="G16:O16"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:O32"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G29:O29"/>
-    <mergeCell ref="G30:O30"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G23:O23"/>
-    <mergeCell ref="G24:O24"/>
-    <mergeCell ref="G25:O25"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G35:O35"/>
-    <mergeCell ref="G36:O36"/>
-    <mergeCell ref="G37:O37"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G33:O33"/>
-    <mergeCell ref="G34:O34"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G17:O17"/>
-    <mergeCell ref="G18:O18"/>
-    <mergeCell ref="G19:O19"/>
-    <mergeCell ref="G31:O31"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G26:O26"/>
-    <mergeCell ref="G27:O27"/>
-    <mergeCell ref="G28:O28"/>
+    <mergeCell ref="D1:M1"/>
+    <mergeCell ref="D2:M2"/>
+    <mergeCell ref="D3:M3"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D5:M5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D83:L83"/>
+    <mergeCell ref="D73:L74"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="D66:G66"/>
+    <mergeCell ref="D69:G69"/>
+    <mergeCell ref="D72:G72"/>
+    <mergeCell ref="D67:L68"/>
+    <mergeCell ref="D70:L71"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J47:L48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="D58:E59"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J58:L59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="D57:L57"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="J51:L51"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:I10"/>
@@ -3340,105 +3370,91 @@
     <mergeCell ref="G21:O21"/>
     <mergeCell ref="G22:O22"/>
     <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="D58:E59"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="J58:L59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="D57:L57"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="J47:L48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="J51:L51"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="D1:M1"/>
-    <mergeCell ref="D2:M2"/>
-    <mergeCell ref="D3:M3"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D5:M5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D83:L83"/>
-    <mergeCell ref="D73:L74"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="D66:G66"/>
-    <mergeCell ref="D69:G69"/>
-    <mergeCell ref="D72:G72"/>
-    <mergeCell ref="D67:L68"/>
-    <mergeCell ref="D70:L71"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G17:O17"/>
+    <mergeCell ref="G18:O18"/>
+    <mergeCell ref="G19:O19"/>
+    <mergeCell ref="G31:O31"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G26:O26"/>
+    <mergeCell ref="G27:O27"/>
+    <mergeCell ref="G28:O28"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G23:O23"/>
+    <mergeCell ref="G24:O24"/>
+    <mergeCell ref="G25:O25"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G35:O35"/>
+    <mergeCell ref="G36:O36"/>
+    <mergeCell ref="G37:O37"/>
+    <mergeCell ref="E9:O9"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="G14:O14"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="G15:O15"/>
+    <mergeCell ref="G16:O16"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G32:O32"/>
+    <mergeCell ref="G33:O33"/>
+    <mergeCell ref="G34:O34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G29:O29"/>
+    <mergeCell ref="G30:O30"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="C38:O40"/>
+    <mergeCell ref="K10:O10"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="M81:O81"/>
+    <mergeCell ref="C76:F80"/>
+    <mergeCell ref="G76:H80"/>
+    <mergeCell ref="I76:J80"/>
+    <mergeCell ref="K76:L80"/>
+    <mergeCell ref="M76:O80"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="F44:L44"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="D35:F35"/>
   </mergeCells>
-  <conditionalFormatting sqref="D83:L83">
-    <cfRule type="containsBlanks" dxfId="3" priority="1">
-      <formula>LEN(TRIM(D83))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F49:L56">
-    <cfRule type="containsBlanks" dxfId="2" priority="3">
+    <cfRule type="containsBlanks" dxfId="6" priority="3">
       <formula>LEN(TRIM(F49))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60:L64">
-    <cfRule type="containsBlanks" dxfId="1" priority="2">
+    <cfRule type="containsBlanks" dxfId="5" priority="2">
       <formula>LEN(TRIM(F60))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10:O10 E11:J11 M11:O11 L13:O13 G14:O22 G26:O37 F42:G42 J42:L42 F43 D67:L68 D70:L71 D73:L74 C81:F81 M81:O81">
-    <cfRule type="containsBlanks" dxfId="0" priority="4">
+    <cfRule type="containsBlanks" dxfId="4" priority="4">
       <formula>LEN(TRIM(C10))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D83:L83">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(D83))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="756" yWindow="874" count="46">
